--- a/ARM Functions/Other Mechanics/Expand Item List.xlsx
+++ b/ARM Functions/Other Mechanics/Expand Item List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA43A36-1E76-4377-9899-5BF4521E632E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FE3472-A8F4-41C6-A457-5D007233820D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1483" yWindow="883" windowWidth="16457" windowHeight="17914" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
   <si>
     <t>00276BA3</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>These change the max size of lookups on the item table</t>
-  </si>
-  <si>
-    <t>Compact table of sprites</t>
   </si>
   <si>
     <t>002084B0</t>
@@ -204,28 +201,58 @@
     <t>Insert additional lines in the appropriate text files for item name and description</t>
   </si>
   <si>
-    <t>002D2B6B in UM</t>
-  </si>
-  <si>
-    <t>0034B43B in UM</t>
-  </si>
-  <si>
     <t>E5</t>
   </si>
   <si>
     <t>E0</t>
   </si>
   <si>
-    <t>0034B437 in UM</t>
-  </si>
-  <si>
-    <t>0034B433 in UM</t>
-  </si>
-  <si>
     <t>0034B433</t>
   </si>
   <si>
     <t>0034B42F</t>
+  </si>
+  <si>
+    <t>US File</t>
+  </si>
+  <si>
+    <t>US Load</t>
+  </si>
+  <si>
+    <t>UM File</t>
+  </si>
+  <si>
+    <t>UM Load</t>
+  </si>
+  <si>
+    <t>002D2B6B</t>
+  </si>
+  <si>
+    <t>0034B43B</t>
+  </si>
+  <si>
+    <t>00276B98</t>
+  </si>
+  <si>
+    <t>00F020E3</t>
+  </si>
+  <si>
+    <t>003BAC00</t>
+  </si>
+  <si>
+    <t>battle.cro edits</t>
+  </si>
+  <si>
+    <t>00061A68</t>
+  </si>
+  <si>
+    <t>00061A74</t>
+  </si>
+  <si>
+    <t>Compact table of sprites (same in both)</t>
+  </si>
+  <si>
+    <t>003BAC08</t>
   </si>
 </sst>
 </file>
@@ -279,12 +306,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -568,311 +598,507 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.23046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.61328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.23046875" style="1"/>
+    <col min="2" max="2" width="14.765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.23046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.61328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.3828125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.23046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f t="shared" ref="B5:B11" si="0">DEC2HEX(HEX2DEC(A5)+HEX2DEC(100000),8)</f>
+        <v>00376B98</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(D5)+HEX2DEC(100000),8)</f>
+        <v>00376B98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>00376BA3</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
+      <c r="D6" s="1" t="str">
+        <f>A6</f>
+        <v>00276BA3</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(D6)+HEX2DEC(100000),8)</f>
+        <v>00376BA3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>003D2B67</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f t="shared" ref="E7:E11" si="1">DEC2HEX(HEX2DEC(D7)+HEX2DEC(100000),8)</f>
+        <v>003D2B6B</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0044B42F</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>0044B433</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0044B433</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="E9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>0044B437</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>0044B437</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>0044B43B</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>66</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>004BAC00</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="str">
-        <f>DEC2HEX(HEX2DEC(A11)+4,8)</f>
-        <v>002083B8</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="1" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A25)-HEX2DEC(A12)-8,"]")</f>
-        <v>ldr r1, [pc, #44]</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="str">
-        <f t="shared" ref="A13:A15" si="0">DEC2HEX(HEX2DEC(A12)+4,8)</f>
-        <v>002083BC</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>002083C0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>002083C4</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>65</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>004BAC08</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="str">
+        <f t="shared" ref="B15:B29" si="2">DEC2HEX(HEX2DEC(A15)+HEX2DEC(100000),8)</f>
+        <v>003083B4</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="str">
         <f>DEC2HEX(HEX2DEC(A15)+4,8)</f>
+        <v>002083B8</v>
+      </c>
+      <c r="B16" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083B8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="1" t="str">
+        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A29)-HEX2DEC(A16)-8,"]")</f>
+        <v>ldr r1, [pc, #44]</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="str">
+        <f t="shared" ref="A17:A19" si="3">DEC2HEX(HEX2DEC(A16)+4,8)</f>
+        <v>002083BC</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083BC</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>002083C0</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083C0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>002083C4</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083C4</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(A19)+4,8)</f>
         <v>002083C8</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B20" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083C8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(A20)+4,8)</f>
+        <v>002083CC</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083CC</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="str">
-        <f>DEC2HEX(HEX2DEC(A16)+4,8)</f>
-        <v>002083CC</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="str">
+        <f t="shared" ref="A22:A29" si="4">DEC2HEX(HEX2DEC(A21)+4,8)</f>
+        <v>002083D0</v>
+      </c>
+      <c r="B22" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083D0</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="str">
-        <f t="shared" ref="A18:A25" si="1">DEC2HEX(HEX2DEC(A17)+4,8)</f>
-        <v>002083D0</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>002083D4</v>
+      </c>
+      <c r="B23" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083D4</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>002083D8</v>
+      </c>
+      <c r="B24" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083D8</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>002083D4</v>
-      </c>
-      <c r="B19" s="2" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>002083DC</v>
+      </c>
+      <c r="B25" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083DC</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>002083E0</v>
+      </c>
+      <c r="B26" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083E0</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>002083D8</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>002083DC</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="D26" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>002083E4</v>
+      </c>
+      <c r="B27" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083E4</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>002083E0</v>
-      </c>
-      <c r="B22" s="2" t="s">
+      <c r="D27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>002083E8</v>
+      </c>
+      <c r="B28" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083E8</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>002083EC</v>
+      </c>
+      <c r="B29" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>003083EC</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>002083E4</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>002083E8</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A25" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>002083EC</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="14.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="1" t="s">
+    </row>
+    <row r="37" spans="1:5" ht="14.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A34" s="1" t="s">
-        <v>54</v>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(A42)+HEX2DEC("6dd000"),8)</f>
+        <v>0073EA68</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" s="1" t="str">
+        <f>DEC2HEX(HEX2DEC(A43)+HEX2DEC("6dd000"),8)</f>
+        <v>0073EA74</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A41:E41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -890,16 +1116,16 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="4" t="str">
         <f>_xlfn.CONCAT(D4:E4)</f>
@@ -926,10 +1152,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>49</v>
       </c>
       <c r="G3" t="str">
         <f>DEC2HEX(G2/2)</f>
@@ -957,7 +1183,7 @@
         <v>000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -14404,7 +14630,7 @@
         <v/>
       </c>
       <c r="C964" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
